--- a/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
+++ b/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
@@ -1,31 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HIZLI_BASLANGIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GIRDI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HAMMADDE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="RECETE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MOTOR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="FIYATLAMA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VARYANS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="VARSAYIMLAR" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="FINANSMAN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SENARYO" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="PANO" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="KARAR" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="KANIT_RAPORU" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="KONTROLLER" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ORNEK_VERI" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="LISTELER" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="AYARLAR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="KILAVUZ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAMMADDE" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECETE" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIYATLAMA" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARYANS" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="18" state="hidden" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="20" state="hidden" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="22" state="hidden" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="raporTarihi">AYARLAR!$B$7</definedName>
@@ -91,9 +94,9 @@
     <definedName name="ListeGuven">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeDuyarlilik">LISTELER!$E$6:$E$8</definedName>
     <definedName name="ListeVersiyon">LISTELER!$G$6:$G$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'KARAR'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'KANIT_RAPORU'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'PANO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'KARAR'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'KANIT_RAPORU'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -101,13 +104,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -247,8 +252,117 @@
       <color rgb="00006100"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -279,8 +393,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -289,11 +421,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -517,6 +663,49 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,13 +826,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -667,7 +856,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -719,13 +908,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -749,7 +938,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -801,13 +990,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -830,14 +1019,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -889,13 +1078,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -919,7 +1108,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -971,13 +1160,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1001,7 +1190,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1053,13 +1242,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1083,7 +1272,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1135,13 +1324,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1165,7 +1354,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1217,13 +1406,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1247,7 +1436,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2934,7 +3123,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2949,9 +3138,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2971,9 +3160,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2993,9 +3182,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3005,7 +3194,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -3020,9 +3209,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3042,9 +3231,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3064,9 +3253,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3086,9 +3275,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3108,9 +3297,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3513,145 +3702,1160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2742"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="78" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KAPAK — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="B2" s="73" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — E-TİCARET KÂRLILIK VE BİRİM EKONOMİSİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Km × araç tipi × dönüş yükü ile net navlun maliyetini hesaplayın; reçete bileşiminden fiyat önerin; hat yatırımı için YATIRIM YAPILIR / YATIRIM YAPMA kararını üretin.</t>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>AYLIK NET CİRO</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="inlineStr">
+        <is>
+          <t>NET KATKI MARJI (CM2)</t>
+        </is>
+      </c>
+      <c r="F6" s="75" t="inlineStr">
+        <is>
+          <t>İADE VE KOMİSYON KAÇAĞI</t>
+        </is>
+      </c>
+      <c r="H6" s="76" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Navlun maliyet reçetesi: hammadde (yakıt) + işçilik + ambalaj + genel gider = %100</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• Fire (boş km) kolonu ve AYARLAR birim dönüşüm tablosu</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="77" t="inlineStr">
+        <is>
+          <t>₺ 6.250.000</t>
+        </is>
+      </c>
+      <c r="D7" s="77" t="inlineStr">
+        <is>
+          <t>% 31,8</t>
+        </is>
+      </c>
+      <c r="F7" s="78" t="inlineStr">
+        <is>
+          <t>MİNİMUM (% 2,1)</t>
+        </is>
+      </c>
+      <c r="H7" s="79" t="inlineStr">
+        <is>
+          <t>Komisyon oranı %22 üzerindeki 4 üründe liste fiyatını güncelle, reklamı karlı gruba kaydır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Dönüş yükü katkısı ile net navlun ve önerilen teklif fiyatı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• CAPEX/OPEX + öz kaynak / kredi + NPV / IRR tornado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• Kötümser YATIRIM YAPMA yolu; boş girişte VERİ YOK</t>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Geçen Aya Göre: +% 18,2 Artış</t>
+        </is>
+      </c>
+      <c r="D9" s="81" t="inlineStr">
+        <is>
+          <t>Komisyon &amp; Kargo Sonrası Gerçek Kâr</t>
+        </is>
+      </c>
+      <c r="F9" s="82" t="inlineStr">
+        <is>
+          <t>Pazaryeri Kesinti Denetimi: TAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="84" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="84" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="84" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="84" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="84" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="84" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="84" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Sevkiyat fiyatlandırma — km ve araç tipine göre teklif satırı</t>
+      <c r="B14" s="85" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="86" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="86" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="87">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="88">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="86" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="89" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="90" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• Lojistik müdürü — hat açılışı ve kârlılık kararı</t>
+      <c r="B15" s="85" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="86" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="86" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="87">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="88">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="86" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="89" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="90" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• CFO — NPV/IRR ve finansman senaryosu</t>
+      <c r="B16" s="85" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="86" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="86" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="87">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="88">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="86" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="89" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="90" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="85" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="86" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="86" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="87">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="88">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="86" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="89" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="90" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
+      <c r="B18" s="85" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="86" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="86" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="87">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="88">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="86" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="89" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="90" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>1) HIZLI_BASLANGIC → 2) GIRDI / HAMMADDE / RECETE sarı hücreler → 3) PANO/KARAR → 4) KANIT_RAPORU yazdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | Kod: SFN-PRO</t>
+      <c r="B19" s="85" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="86" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="86" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="87">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="88">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="86" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="89" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="90" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="8">
-    <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A8:AD8"/>
-    <mergeCell ref="A7:AD7"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A11:AD11"/>
-    <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A19:P19"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C65911"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FIYATLAMA — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Fiyat önerisi ve rakip bandı</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Net navlun [₺]</t>
+        </is>
+      </c>
+      <c r="B5" s="18">
+        <f>sfn_netNavlun</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Hedef marj</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>GIRDI!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>Önerilen teklif [₺]</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>IFERROR(MOTOR!G38,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Km başı teklif [₺]</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>IFERROR(IF(GIRDI!B8=0,0,B7/GIRDI!B8),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Ton başı teklif [₺]</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>IFERROR(IF(GIRDI!B10=0,0,B7/GIRDI!B10),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Rakip düşük [₺]</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Rakip yüksek [₺]</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Konum</t>
+        </is>
+      </c>
+      <c r="B13" s="43">
+        <f>IF(OR(B7&lt;=0,COUNTA(tblGirdi[Alan Anahtarı])=0),"VERİ YOK",IF(B7&lt;B11,"DÜŞÜK",IF(B7&gt;B12,"YÜKSEK","BAND İÇİ")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(SEARCH("VERİ YOK",B13))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="4">
+      <formula>ISNUMBER(SEARCH("DÜŞÜK",B13))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>ISNUMBER(SEARCH("BAND",B13))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B11:B12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Negatif olamaz." promptTitle="Rakip" prompt="0 ve üzeri TL." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000000</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VARYANS — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Reçete versiyon varyans köprüsü (V0 → V1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Kalem</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>V0 maliyet</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>V1 maliyet</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>Fiyat etkisi</t>
+        </is>
+      </c>
+      <c r="E5" s="45" t="inlineStr">
+        <is>
+          <t>Miktar etkisi</t>
+        </is>
+      </c>
+      <c r="F5" s="45" t="inlineStr">
+        <is>
+          <t>Karışım etkisi</t>
+        </is>
+      </c>
+      <c r="G5" s="45" t="inlineStr">
+        <is>
+          <t>Toplam fark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Hammadde (yakıt)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C6" s="18">
+        <f>IFERROR(MOTOR!G30,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>IFERROR((C6-B6)*sfn_varyansFiyatPay,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="18">
+        <f>IFERROR((C6-B6)*sfn_varyansMiktarPay,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>IFERROR((C6-B6)*sfn_varyansKarisimPay,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>IFERROR(C6-B6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>İşçilik</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C7" s="18">
+        <f>IFERROR(MOTOR!G31,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>IFERROR((C7-B7)*sfn_varyansFiyatPay,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>IFERROR((C7-B7)*sfn_varyansMiktarPay,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>IFERROR((C7-B7)*sfn_varyansKarisimPay,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>IFERROR(C7-B7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Ambalaj</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="18">
+        <f>IFERROR(MOTOR!G32,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>IFERROR((C8-B8)*sfn_varyansFiyatPay,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>IFERROR((C8-B8)*sfn_varyansMiktarPay,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>IFERROR((C8-B8)*sfn_varyansKarisimPay,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>IFERROR(C8-B8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Genel gider V0 tutar</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C9" s="18">
+        <f>IFERROR(MOTOR!G33,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="18">
+        <f>IFERROR((C9-B9)*sfn_varyansFiyatPay,0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>IFERROR((C9-B9)*sfn_varyansMiktarPay,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>IFERROR((C9-B9)*sfn_varyansKarisimPay,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>IFERROR(C9-B9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Varyans köprü toplam</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>IFERROR(SUM(G6:G9),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Versiyon köprüsü özeti</t>
+        </is>
+      </c>
+      <c r="B12" s="42">
+        <f>_xlfn.TEXTJOIN(" | ",TRUE,"V0→V1 fark ",TEXT(B11,"₺ #,##0")," · fiyat ",TEXT(SUM(D6:D9),"₺ #,##0")," · miktar ",TEXT(SUM(E6:E9),"₺ #,##0")," · karışım ",TEXT(SUM(F6:F9),"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G6:G9">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B6:B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Negatif olamaz." promptTitle="V0 maliyet" prompt="Eski versiyon tutarı." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000000</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VARSAYIMLAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Varsayımlar — her satırda kaynak ve güven</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>varsayim_id</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>aciklama</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>deger</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>birim</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>kaynak</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>guven</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>duyarlilik</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>kontrol</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>V-01</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Yakıt birim fiyat</t>
+        </is>
+      </c>
+      <c r="C6" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>₺/L</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Akaryakıt piyasa</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>sert</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>yüksek</t>
+        </is>
+      </c>
+      <c r="H6" s="22">
+        <f>IF($A6="","",IF(OR($E6="",$F6=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>V-02</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Tüketim L/100km</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Araç üretici kartı</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>sert</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>yüksek</t>
+        </is>
+      </c>
+      <c r="H7" s="22">
+        <f>IF($A7="","",IF(OR($E7="",$F7=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>V-03</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Dönüş yükü oranı</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>oran</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Operasyon geçmişi</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>yumuşak</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>yüksek</t>
+        </is>
+      </c>
+      <c r="H8" s="22">
+        <f>IF($A8="","",IF(OR($E8="",$F8=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>V-04</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Hedef marj</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>oran</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Satış politikası</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>sert</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="H9" s="22">
+        <f>IF($A9="","",IF(OR($E9="",$F9=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>V-05</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>oran</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Finans / yönetim</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>yumuşak</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>yüksek</t>
+        </is>
+      </c>
+      <c r="H10" s="22">
+        <f>IF($A10="","",IF(OR($E10="",$F10=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>V-06</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Yıllık sefer</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Hat planı</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>yumuşak</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="H11" s="22">
+        <f>IF($A11="","",IF(OR($E11="",$F11=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>V-07</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>CAPEX araç</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>₺</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Satın alma teklifi</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>sert</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="H12" s="22">
+        <f>IF($A12="","",IF(OR($E12="",$F12=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>V-08</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Fire boş km</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>oran</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Saha ölçümü</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>yumuşak</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="H13" s="22">
+        <f>IF($A13="","",IF(OR($E13="",$F13=""),"EKSİK","TAM"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H6:H13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>H6="EKSİK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>H6="TAM"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="F6:F13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="sert/yumuşak." promptTitle="Güven" prompt="sert veya yumuşak." type="list" errorStyle="stop">
+      <formula1>ListeGuven</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Listeden seçin." promptTitle="Duyarlılık" prompt="yüksek / orta / düşük." type="list" errorStyle="stop">
+      <formula1>ListeDuyarlilik</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C65911"/>
@@ -3806,7 +5010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -4254,7 +5458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -4920,7 +6124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B3261E"/>
@@ -5090,7 +6294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -5329,7 +6533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -5497,7 +6701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -11735,7 +12939,253 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="91" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="92" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="92" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="92" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="93" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="85" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="95" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="93" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="94" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="85" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="95" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="93" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="94" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="85" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="95" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="93" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="94" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="85" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="95" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="93" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="85" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="95" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="93" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="94" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="85" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -11852,7 +13302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -18844,7 +20294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -18976,7 +20426,234 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="91" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="96" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="97" t="inlineStr">
+        <is>
+          <t>Tüm pazaryeri komisyon ve kargo baremleri net marj analiziyle eşleştirilmiş, negatif karlı ürünler elenmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="96" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="97" t="inlineStr">
+        <is>
+          <t>Kargo maliyetleri %20 artsa dahi birim sipariş başına net kâr pozitif kalmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="96" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="93" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="93" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Km × araç tipi × dönüş yükü ile net navlun maliyetini hesaplayın; reçete bileşiminden fiyat önerin; hat yatırımı için YATIRIM YAPILIR / YATIRIM YAPMA kararını üretin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• Navlun maliyet reçetesi: hammadde (yakıt) + işçilik + ambalaj + genel gider = %100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• Fire (boş km) kolonu ve AYARLAR birim dönüşüm tablosu</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• Dönüş yükü katkısı ile net navlun ve önerilen teklif fiyatı</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• CAPEX/OPEX + öz kaynak / kredi + NPV / IRR tornado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• Kötümser YATIRIM YAPMA yolu; boş girişte VERİ YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• Sevkiyat fiyatlandırma — km ve araç tipine göre teklif satırı</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• Lojistik müdürü — hat açılışı ve kârlılık kararı</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• CFO — NPV/IRR ve finansman senaryosu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>1) HIZLI_BASLANGIC → 2) GIRDI / HAMMADDE / RECETE sarı hücreler → 3) PANO/KARAR → 4) KANIT_RAPORU yazdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | Kod: SFN-PRO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="8">
+    <mergeCell ref="A9:AD9"/>
+    <mergeCell ref="A8:AD8"/>
+    <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A11:AD11"/>
+    <mergeCell ref="A10:AD10"/>
+    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A19:P19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -19074,7 +20751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -25683,7 +27360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -32039,7 +33716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -38321,7 +39998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -40705,804 +42382,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C65911"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FIYATLAMA — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Fiyat önerisi ve rakip bandı</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>Net navlun [₺]</t>
-        </is>
-      </c>
-      <c r="B5" s="18">
-        <f>sfn_netNavlun</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Hedef marj</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>GIRDI!B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>Önerilen teklif [₺]</t>
-        </is>
-      </c>
-      <c r="B7" s="17">
-        <f>IFERROR(MOTOR!G38,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Km başı teklif [₺]</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>IFERROR(IF(GIRDI!B8=0,0,B7/GIRDI!B8),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Ton başı teklif [₺]</t>
-        </is>
-      </c>
-      <c r="B9" s="18">
-        <f>IFERROR(IF(GIRDI!B10=0,0,B7/GIRDI!B10),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Rakip düşük [₺]</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>Rakip yüksek [₺]</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>Konum</t>
-        </is>
-      </c>
-      <c r="B13" s="43">
-        <f>IF(OR(B7&lt;=0,COUNTA(tblGirdi[Alan Anahtarı])=0),"VERİ YOK",IF(B7&lt;B11,"DÜŞÜK",IF(B7&gt;B12,"YÜKSEK","BAND İÇİ")))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B13))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="4">
-      <formula>ISNUMBER(SEARCH("DÜŞÜK",B13))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>ISNUMBER(SEARCH("BAND",B13))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="cellIs" priority="4" operator="lessThanOrEqual" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="B11:B12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Negatif olamaz." promptTitle="Rakip" prompt="0 ve üzeri TL." type="decimal" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>100000000</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VARYANS — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Reçete versiyon varyans köprüsü (V0 → V1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>V0 maliyet</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>V1 maliyet</t>
-        </is>
-      </c>
-      <c r="D5" s="45" t="inlineStr">
-        <is>
-          <t>Fiyat etkisi</t>
-        </is>
-      </c>
-      <c r="E5" s="45" t="inlineStr">
-        <is>
-          <t>Miktar etkisi</t>
-        </is>
-      </c>
-      <c r="F5" s="45" t="inlineStr">
-        <is>
-          <t>Karışım etkisi</t>
-        </is>
-      </c>
-      <c r="G5" s="45" t="inlineStr">
-        <is>
-          <t>Toplam fark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Hammadde (yakıt)</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>9500</v>
-      </c>
-      <c r="C6" s="18">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="18">
-        <f>IFERROR((C6-B6)*sfn_varyansFiyatPay,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="18">
-        <f>IFERROR((C6-B6)*sfn_varyansMiktarPay,0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="18">
-        <f>IFERROR((C6-B6)*sfn_varyansKarisimPay,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="18">
-        <f>IFERROR(C6-B6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>İşçilik</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C7" s="18">
-        <f>IFERROR(MOTOR!G31,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="18">
-        <f>IFERROR((C7-B7)*sfn_varyansFiyatPay,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="18">
-        <f>IFERROR((C7-B7)*sfn_varyansMiktarPay,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="18">
-        <f>IFERROR((C7-B7)*sfn_varyansKarisimPay,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="18">
-        <f>IFERROR(C7-B7,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Ambalaj</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" s="18">
-        <f>IFERROR(MOTOR!G32,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="18">
-        <f>IFERROR((C8-B8)*sfn_varyansFiyatPay,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="18">
-        <f>IFERROR((C8-B8)*sfn_varyansMiktarPay,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="18">
-        <f>IFERROR((C8-B8)*sfn_varyansKarisimPay,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="18">
-        <f>IFERROR(C8-B8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Genel gider V0 tutar</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>2250</v>
-      </c>
-      <c r="C9" s="18">
-        <f>IFERROR(MOTOR!G33,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="18">
-        <f>IFERROR((C9-B9)*sfn_varyansFiyatPay,0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="18">
-        <f>IFERROR((C9-B9)*sfn_varyansMiktarPay,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="18">
-        <f>IFERROR((C9-B9)*sfn_varyansKarisimPay,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="18">
-        <f>IFERROR(C9-B9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Varyans köprü toplam</t>
-        </is>
-      </c>
-      <c r="B11" s="18">
-        <f>IFERROR(SUM(G6:G9),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>Versiyon köprüsü özeti</t>
-        </is>
-      </c>
-      <c r="B12" s="42">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE,"V0→V1 fark ",TEXT(B11,"₺ #,##0")," · fiyat ",TEXT(SUM(D6:D9),"₺ #,##0")," · miktar ",TEXT(SUM(E6:E9),"₺ #,##0")," · karışım ",TEXT(SUM(F6:F9),"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G6:G9">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="B6:B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Negatif olamaz." promptTitle="V0 maliyet" prompt="Eski versiyon tutarı." type="decimal" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>100000000</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VARSAYIMLAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Varsayımlar — her satırda kaynak ve güven</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>varsayim_id</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>aciklama</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>deger</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>birim</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>kaynak</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>guven</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>duyarlilik</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>kontrol</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>V-01</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Yakıt birim fiyat</t>
-        </is>
-      </c>
-      <c r="C6" s="68" t="n">
-        <v>45</v>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>₺/L</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Akaryakıt piyasa</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>sert</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>yüksek</t>
-        </is>
-      </c>
-      <c r="H6" s="22">
-        <f>IF($A6="","",IF(OR($E6="",$F6=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>V-02</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Tüketim L/100km</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Araç üretici kartı</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>sert</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>yüksek</t>
-        </is>
-      </c>
-      <c r="H7" s="22">
-        <f>IF($A7="","",IF(OR($E7="",$F7=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>V-03</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Dönüş yükü oranı</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>oran</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Operasyon geçmişi</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>yumuşak</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>yüksek</t>
-        </is>
-      </c>
-      <c r="H8" s="22">
-        <f>IF($A8="","",IF(OR($E8="",$F8=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>V-04</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Hedef marj</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>oran</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Satış politikası</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>sert</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>orta</t>
-        </is>
-      </c>
-      <c r="H9" s="22">
-        <f>IF($A9="","",IF(OR($E9="",$F9=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>V-05</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>oran</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Finans / yönetim</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>yumuşak</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>yüksek</t>
-        </is>
-      </c>
-      <c r="H10" s="22">
-        <f>IF($A10="","",IF(OR($E10="",$F10=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>V-06</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Yıllık sefer</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>adet</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Hat planı</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>yumuşak</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>orta</t>
-        </is>
-      </c>
-      <c r="H11" s="22">
-        <f>IF($A11="","",IF(OR($E11="",$F11=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>V-07</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>CAPEX araç</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>₺</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Satın alma teklifi</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>sert</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>orta</t>
-        </is>
-      </c>
-      <c r="H12" s="22">
-        <f>IF($A12="","",IF(OR($E12="",$F12=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>V-08</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Fire boş km</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>oran</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Saha ölçümü</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>yumuşak</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>orta</t>
-        </is>
-      </c>
-      <c r="H13" s="22">
-        <f>IF($A13="","",IF(OR($E13="",$F13=""),"EKSİK","TAM"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H6:H13">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>H6="EKSİK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>H6="TAM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="F6:F13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="sert/yumuşak." promptTitle="Güven" prompt="sert veya yumuşak." type="list" errorStyle="stop">
-      <formula1>ListeGuven</formula1>
-    </dataValidation>
-    <dataValidation sqref="G6:G13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Listeden seçin." promptTitle="Duyarlılık" prompt="yüksek / orta / düşük." type="list" errorStyle="stop">
-      <formula1>ListeDuyarlilik</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
+++ b/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
@@ -7,28 +7,27 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAMMADDE" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECETE" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIYATLAMA" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARYANS" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="22" state="hidden" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAMMADDE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECETE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIYATLAMA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARYANS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VARSAYIMLAR" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINANSMAN" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="raporTarihi">AYARLAR!$B$7</definedName>
@@ -94,9 +93,8 @@
     <definedName name="ListeGuven">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeDuyarlilik">LISTELER!$E$6:$E$8</definedName>
     <definedName name="ListeVersiyon">LISTELER!$G$6:$G$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'KARAR'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'KANIT_RAPORU'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'KARAR'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'KANIT_RAPORU'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -104,15 +102,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="75">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -361,8 +360,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -411,8 +592,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -435,11 +682,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -706,6 +1042,163 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="64" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="63" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="63" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="65" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="10" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1045,416 +1538,6 @@
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Maliyet Kırılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$23:$A$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$23:$B$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NPV Senaryo</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$23:$D$25</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$23:$E$25</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Güven / Risk</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$29:$A$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$29:$B$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Brüt / Net Navlun</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$29:$D$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$29:$E$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Km Basina Maliyet</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B32</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$33:$A$34</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$33:$B$34</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -3193,121 +3276,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGirdi" displayName="tblGirdi" ref="A25:F1024" headerRowCount="1">
   <tableColumns count="6">
@@ -3705,351 +3673,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="73" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — E-TİCARET KÂRLILIK VE BİRİM EKONOMİSİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="74" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="98" t="inlineStr">
+        <is>
+          <t>SEVKIYAT FIYATLAMA NAVLUN — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="99" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="100" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="101" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="102" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="103" t="n"/>
+      <c r="D5" s="104" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="105" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="103" t="n"/>
+      <c r="G5" s="106" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="102" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="103" t="n"/>
+      <c r="J5" s="107" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="108" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="103" t="n"/>
+      <c r="M5" s="104" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="75" t="inlineStr">
-        <is>
-          <t>AYLIK NET CİRO</t>
-        </is>
-      </c>
-      <c r="D6" s="75" t="inlineStr">
-        <is>
-          <t>NET KATKI MARJI (CM2)</t>
-        </is>
-      </c>
-      <c r="F6" s="75" t="inlineStr">
-        <is>
-          <t>İADE VE KOMİSYON KAÇAĞI</t>
-        </is>
-      </c>
-      <c r="H6" s="76" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="109" t="n"/>
+      <c r="C6" s="103" t="n"/>
+      <c r="D6" s="103" t="n"/>
+      <c r="E6" s="110" t="n"/>
+      <c r="F6" s="103" t="n"/>
+      <c r="G6" s="103" t="n"/>
+      <c r="H6" s="109" t="n"/>
+      <c r="I6" s="103" t="n"/>
+      <c r="J6" s="103" t="n"/>
+      <c r="K6" s="111" t="n"/>
+      <c r="L6" s="103" t="n"/>
+      <c r="M6" s="103" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="77" t="inlineStr">
-        <is>
-          <t>₺ 6.250.000</t>
-        </is>
-      </c>
-      <c r="D7" s="77" t="inlineStr">
-        <is>
-          <t>% 31,8</t>
-        </is>
-      </c>
-      <c r="F7" s="78" t="inlineStr">
-        <is>
-          <t>MİNİMUM (% 2,1)</t>
-        </is>
-      </c>
-      <c r="H7" s="79" t="inlineStr">
-        <is>
-          <t>Komisyon oranı %22 üzerindeki 4 üründe liste fiyatını güncelle, reklamı karlı gruba kaydır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="112" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="103" t="n"/>
+      <c r="D7" s="103" t="n"/>
+      <c r="E7" s="113" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="103" t="n"/>
+      <c r="G7" s="103" t="n"/>
+      <c r="H7" s="112" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="103" t="n"/>
+      <c r="J7" s="103" t="n"/>
+      <c r="K7" s="114" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="103" t="n"/>
+      <c r="M7" s="103" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="109" t="n"/>
+      <c r="C8" s="103" t="n"/>
+      <c r="D8" s="103" t="n"/>
+      <c r="E8" s="110" t="n"/>
+      <c r="F8" s="103" t="n"/>
+      <c r="G8" s="103" t="n"/>
+      <c r="H8" s="109" t="n"/>
+      <c r="I8" s="103" t="n"/>
+      <c r="J8" s="103" t="n"/>
+      <c r="K8" s="111" t="n"/>
+      <c r="L8" s="103" t="n"/>
+      <c r="M8" s="103" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="80" t="inlineStr">
-        <is>
-          <t>Geçen Aya Göre: +% 18,2 Artış</t>
-        </is>
-      </c>
-      <c r="D9" s="81" t="inlineStr">
-        <is>
-          <t>Komisyon &amp; Kargo Sonrası Gerçek Kâr</t>
-        </is>
-      </c>
-      <c r="F9" s="82" t="inlineStr">
-        <is>
-          <t>Pazaryeri Kesinti Denetimi: TAM</t>
+      <c r="B9" s="115" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="103" t="n"/>
+      <c r="D9" s="103" t="n"/>
+      <c r="E9" s="116" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="103" t="n"/>
+      <c r="G9" s="103" t="n"/>
+      <c r="H9" s="115" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="103" t="n"/>
+      <c r="J9" s="103" t="n"/>
+      <c r="K9" s="117" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="103" t="n"/>
+      <c r="M9" s="103" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="96" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="118" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="96" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="83" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="84" t="inlineStr">
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="95" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="119" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="84" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="84" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="84" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="84" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="84" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="84" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="84" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="85" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="86" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="86" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="87">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="88">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="86" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="89" t="n">
+      <c r="C14" s="119" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="119" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="119" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="120" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="120" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="120" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="120" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="120" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="95" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="95" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="95" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="95" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="121" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="121" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="122" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="123" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="107" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="95" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="95" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="95" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="95" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="121" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="121" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="122" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="123" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="104" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="95" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="95" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="95" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="95" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="121" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="121" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="122" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="123" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="124" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="95" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="95" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="95" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="95" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="121" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="121" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="122" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="123" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="107" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="95" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="95" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="95" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="95" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="125" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="126" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="127" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="128" t="inlineStr"/>
+      <c r="L19" s="129" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="95" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="95" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="90" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="85" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="86" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="86" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="87">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="88">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="86" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="89" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="90" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="85" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="86" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="86" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="87">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="88">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="86" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="89" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="90" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="85" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="86" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="86" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="87">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="88">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="86" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="89" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="90" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="85" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="86" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="86" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="87">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="88">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="86" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="89" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="90" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="85" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="86" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="86" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="87">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="88">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="86" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="89" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="90" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="95" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="95" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="130" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="130" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="131" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="132" t="n"/>
+      <c r="M22" s="132" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="80" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="133" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="134" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="132" t="n"/>
+      <c r="M23" s="132" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="81" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="95" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="133" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="135" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="136" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="80" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="137" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="138" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="139" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5461,672 +5653,6 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
-        <is>
-          <t>Karar panosu</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Birim maliyet</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Net navlun</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Dönüş katkı</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Önerilen fiyat</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Km başı</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>Marj hedef</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>Bileşim %</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
-        <is>
-          <t>Tahmin</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="inlineStr">
-        <is>
-          <t>Alarm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="50">
-        <f>IFERROR(sfn_birimMaliyet,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="50">
-        <f>IFERROR(sfn_netNavlun,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="50">
-        <f>IFERROR(sfn_donusYukuKatki,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="50">
-        <f>IFERROR(MOTOR!G38,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="50">
-        <f>IFERROR(MOTOR!G39,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="50">
-        <f>IFERROR(sfn_npv,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="51">
-        <f>IFERROR(sfn_irr,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="51">
-        <f>IFERROR(GIRDI!B12,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="52">
-        <f>IFERROR(MOTOR!G50,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="52">
-        <f>IFERROR(MOTOR!G51,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="51">
-        <f>IFERROR(MOTOR!G45,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="50">
-        <f>IFERROR(sfn_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="N4" s="53">
-        <f>IFERROR(sfn_bilesimAlarm,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Karar özeti</t>
-        </is>
-      </c>
-      <c r="B6" s="54">
-        <f>sfn_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="42">
-        <f>sfn_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Bileşim %100 alarm</t>
-        </is>
-      </c>
-      <c r="B8" s="33">
-        <f>IFERROR(RECETE!B14,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="inlineStr">
-        <is>
-          <t>Yorum</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="55" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Navlun birim maliyet</t>
-        </is>
-      </c>
-      <c r="C11" s="18">
-        <f>IFERROR(sfn_birimMaliyet,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="42">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Birim ",TEXT(C11,"₺ #,##0")," — net ",TEXT(sfn_netNavlun,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="55" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Dönüş yükü katkısı</t>
-        </is>
-      </c>
-      <c r="C12" s="18">
-        <f>IFERROR(sfn_donusYukuKatki,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="42">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Dönüş katkı ",TEXT(C12,"₺ #,##0")," · oran ",TEXT(GIRDI!B11,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="55" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Marj sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="18">
-        <f>IFERROR(ABS(MOTOR!G38-sfn_netNavlun)-sfn_netNavlun*GIRDI!B12,0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="42">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Marj sapma göstergesi ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="55" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Duyarlılık / tornado</t>
-        </is>
-      </c>
-      <c r="C14" s="43">
-        <f>IFERROR(sfn_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="42">
-        <f>IFERROR(sfn_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="55" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo motoru</t>
-        </is>
-      </c>
-      <c r="C15" s="18">
-        <f>IFERROR(sfn_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="42">
-        <f>IFERROR(sfn_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="55" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Maliyet yoğunlaşması</t>
-        </is>
-      </c>
-      <c r="C16" s="31">
-        <f>IFERROR(MOTOR!G60,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="42">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Yakıt/brüt ",TEXT(C16,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="55" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru</t>
-        </is>
-      </c>
-      <c r="C17" s="19">
-        <f>IFERROR(MOTOR!G50,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="42">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Giriş güven skoru ",TEXT(C17,"0"),"/100")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="55" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin + aralık</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>IFERROR(sfn_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="42">
-        <f>IFERROR(sfn_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="55" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Navlun yüzdelik P90</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>IFERROR(IF(COUNT(SENARYO!B6:B8)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!B6:B8,sfn_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="42">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 net ",TEXT(C19,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="56" t="inlineStr">
-        <is>
-          <t>PanoDemoKirilim</t>
-        </is>
-      </c>
-      <c r="D22" s="57" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="E22" s="56" t="inlineStr">
-        <is>
-          <t>PanoDemoNpv</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Hammadde pay</t>
-        </is>
-      </c>
-      <c r="B23" s="58" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="E23" s="47" t="n">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Iscilik pay</t>
-        </is>
-      </c>
-      <c r="B24" s="58" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="E24" s="47" t="n">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Ambalaj pay</t>
-        </is>
-      </c>
-      <c r="B25" s="58" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="E25" s="47" t="n">
-        <v>-280000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Genel pay orani</t>
-        </is>
-      </c>
-      <c r="B26" s="58" t="n">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="57" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="B28" s="56" t="inlineStr">
-        <is>
-          <t>RiskDemo</t>
-        </is>
-      </c>
-      <c r="D28" s="57" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="E28" s="56" t="inlineStr">
-        <is>
-          <t>NavlunDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="57" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="B29" s="59" t="n">
-        <v>100</v>
-      </c>
-      <c r="D29" s="57" t="inlineStr">
-        <is>
-          <t>Brüt</t>
-        </is>
-      </c>
-      <c r="E29" s="47" t="n">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="57" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="B30" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="D30" s="57" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="E30" s="47" t="n">
-        <v>13200</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="57" t="inlineStr">
-        <is>
-          <t>KmDemo</t>
-        </is>
-      </c>
-      <c r="B32" s="56" t="inlineStr">
-        <is>
-          <t>KmBasina</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="57" t="inlineStr">
-        <is>
-          <t>Gidis</t>
-        </is>
-      </c>
-      <c r="B33" s="47" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="57" t="inlineStr">
-        <is>
-          <t>Donus</t>
-        </is>
-      </c>
-      <c r="B34" s="47" t="n">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="B7:H7"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("YATIRIM YAPMA",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>ISNUMBER(SEARCH("YATIRIM YAPILIR",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>ISNUMBER(SEARCH("ALARM",B8))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="cellIs" priority="15" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4">
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4">
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4">
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LSevkiyat Fiyatlama &amp; Navlun Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LSevkiyat Fiyatlama &amp; Navlun Maliyet Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="00B3261E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -6294,7 +5820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -6533,7 +6059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -6701,7 +6227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -12939,253 +12465,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="91" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="92" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="92" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="92" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="92" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="92" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="92" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="93" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="94" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="85" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="95" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="93" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="94" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="85" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="95" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="93" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="94" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="85" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="95" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="93" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="94" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="85" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="95" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="93" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="94" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="85" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="95" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="93" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="94" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="85" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="95" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -13302,7 +12582,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="140" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="141" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="142" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="143" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="143" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="143" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="143" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="143" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="143" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="143" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="143" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="144" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="145" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="146" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="147" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="149">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="146" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="150" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="151" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="152" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="153" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="154" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="156">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="153" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="157" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="144" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="145" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="146" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="147" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="148" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="149">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="146" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="150" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="151" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="152" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="153" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="154" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="156">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="153" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="158" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="144" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="145" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="146" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="147" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="149">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="146" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="150" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="151" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="152" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="153" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="154" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="156">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="153" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="159" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="144" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="145" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="146" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="147" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="149">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="146" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="150" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="151" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="152" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="153" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="154" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="156">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="153" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="158" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="144" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="145" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="146" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="147" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="149">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="146" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="150" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="151" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="152" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="153" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="154" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="156">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="153" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="158" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="160" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="128" t="n"/>
+      <c r="D17" s="128" t="n"/>
+      <c r="E17" s="161">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="128" t="n"/>
+      <c r="G17" s="128" t="n"/>
+      <c r="H17" s="128" t="n"/>
+      <c r="I17" s="128" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -20294,7 +20052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -20432,81 +20190,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="91" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="96" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="162" t="inlineStr">
+        <is>
+          <t>SEVKIYAT FIYATLAMA NAVLUN — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="163" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="164" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="97" t="inlineStr">
-        <is>
-          <t>Tüm pazaryeri komisyon ve kargo baremleri net marj analiziyle eşleştirilmiş, negatif karlı ürünler elenmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="165" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="103" t="n"/>
+      <c r="D6" s="103" t="n"/>
+      <c r="E6" s="103" t="n"/>
+      <c r="F6" s="103" t="n"/>
+      <c r="H6" s="166" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="103" t="n"/>
+      <c r="J6" s="103" t="n"/>
+      <c r="K6" s="103" t="n"/>
+      <c r="L6" s="103" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="103" t="n"/>
+      <c r="C7" s="103" t="n"/>
+      <c r="D7" s="103" t="n"/>
+      <c r="E7" s="103" t="n"/>
+      <c r="F7" s="103" t="n"/>
+      <c r="H7" s="103" t="n"/>
+      <c r="I7" s="103" t="n"/>
+      <c r="J7" s="103" t="n"/>
+      <c r="K7" s="103" t="n"/>
+      <c r="L7" s="103" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="167" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="103" t="n"/>
+      <c r="D8" s="103" t="n"/>
+      <c r="E8" s="168" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="103" t="n"/>
+      <c r="H8" s="167" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="103" t="n"/>
+      <c r="J8" s="103" t="n"/>
+      <c r="K8" s="169" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="103" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="96" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="167" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="103" t="n"/>
+      <c r="D9" s="103" t="n"/>
+      <c r="E9" s="170" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="103" t="n"/>
+      <c r="H9" s="167" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="103" t="n"/>
+      <c r="J9" s="103" t="n"/>
+      <c r="K9" s="170" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="103" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="97" t="inlineStr">
-        <is>
-          <t>Kargo maliyetleri %20 artsa dahi birim sipariş başına net kâr pozitif kalmaktadır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="167" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="103" t="n"/>
+      <c r="D10" s="103" t="n"/>
+      <c r="E10" s="171" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="103" t="n"/>
+      <c r="H10" s="167" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="103" t="n"/>
+      <c r="J10" s="103" t="n"/>
+      <c r="K10" s="171" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="103" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="167" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="103" t="n"/>
+      <c r="D11" s="103" t="n"/>
+      <c r="E11" s="171" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="103" t="n"/>
+      <c r="H11" s="167" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="103" t="n"/>
+      <c r="J11" s="103" t="n"/>
+      <c r="K11" s="171" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="103" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="103" t="n"/>
+      <c r="C12" s="103" t="n"/>
+      <c r="D12" s="103" t="n"/>
+      <c r="E12" s="103" t="n"/>
+      <c r="F12" s="103" t="n"/>
+      <c r="H12" s="103" t="n"/>
+      <c r="I12" s="103" t="n"/>
+      <c r="J12" s="103" t="n"/>
+      <c r="K12" s="103" t="n"/>
+      <c r="L12" s="103" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="103" t="n"/>
+      <c r="C13" s="103" t="n"/>
+      <c r="D13" s="103" t="n"/>
+      <c r="E13" s="103" t="n"/>
+      <c r="F13" s="103" t="n"/>
+      <c r="H13" s="103" t="n"/>
+      <c r="I13" s="103" t="n"/>
+      <c r="J13" s="103" t="n"/>
+      <c r="K13" s="103" t="n"/>
+      <c r="L13" s="103" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="172" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="103" t="n"/>
+      <c r="D14" s="103" t="n"/>
+      <c r="E14" s="103" t="n"/>
+      <c r="F14" s="103" t="n"/>
+      <c r="H14" s="173" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="103" t="n"/>
+      <c r="J14" s="103" t="n"/>
+      <c r="K14" s="103" t="n"/>
+      <c r="L14" s="103" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="93" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="93" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="103" t="n"/>
+      <c r="C15" s="103" t="n"/>
+      <c r="D15" s="103" t="n"/>
+      <c r="E15" s="103" t="n"/>
+      <c r="F15" s="103" t="n"/>
+      <c r="H15" s="103" t="n"/>
+      <c r="I15" s="103" t="n"/>
+      <c r="J15" s="103" t="n"/>
+      <c r="K15" s="103" t="n"/>
+      <c r="L15" s="103" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="130" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="130" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="130" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="130" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
+++ b/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
@@ -108,7 +108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
@@ -116,6 +116,7 @@
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="89">
     <font>
@@ -1178,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1673,6 +1674,24 @@
     </xf>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="48" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="51" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="52" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="55" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="56" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="74" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="44" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="71" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="71" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -27377,7 +27396,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -27393,7 +27412,7 @@
     <row r="2">
       <c r="B2" s="98" t="inlineStr">
         <is>
-          <t>SEVKIYAT FIYATLAMA NAVLUN — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU</t>
         </is>
       </c>
       <c r="L2" s="99" t="inlineStr">
@@ -27410,36 +27429,36 @@
     <row r="3">
       <c r="B3" s="101" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: Lojistik müdürü, sevkiyat fiyatlandırma, filo planlama, CFO · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="102" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>NAVLUN BIRIM MALIYET</t>
         </is>
       </c>
       <c r="C5" s="103" t="n"/>
       <c r="D5" s="104" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="105" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>DÖNÜŞ YÜKÜ KATKISI</t>
         </is>
       </c>
       <c r="F5" s="103" t="n"/>
       <c r="G5" s="106" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="102" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="103" t="n"/>
@@ -27475,31 +27494,27 @@
       <c r="M6" s="103" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="112" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="199">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="103" t="n"/>
       <c r="D7" s="103" t="n"/>
-      <c r="E7" s="113" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="200">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="103" t="n"/>
       <c r="G7" s="103" t="n"/>
-      <c r="H7" s="112" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="199">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="103" t="n"/>
       <c r="J7" s="103" t="n"/>
-      <c r="K7" s="114" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="114">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="103" t="n"/>
       <c r="M7" s="103" t="n"/>
@@ -27521,28 +27536,28 @@
     <row r="9">
       <c r="B9" s="115" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="103" t="n"/>
       <c r="D9" s="103" t="n"/>
       <c r="E9" s="116" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="103" t="n"/>
       <c r="G9" s="103" t="n"/>
       <c r="H9" s="115" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="103" t="n"/>
       <c r="J9" s="103" t="n"/>
       <c r="K9" s="117" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="103" t="n"/>
@@ -27551,7 +27566,7 @@
     <row r="11">
       <c r="B11" s="96" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="118" t="inlineStr">
@@ -27568,7 +27583,7 @@
     <row r="12">
       <c r="B12" s="95" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="95" t="inlineStr">
@@ -27641,18 +27656,16 @@
       </c>
       <c r="H15" s="121" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="121" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="122" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="201">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="202">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="123" t="inlineStr">
         <is>
@@ -27682,18 +27695,16 @@
       </c>
       <c r="H16" s="121" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="121" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="122" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="201">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="202">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="123" t="inlineStr">
         <is>
@@ -27723,18 +27734,16 @@
       </c>
       <c r="H17" s="121" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="121" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="122" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="201">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="202">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="123" t="inlineStr">
         <is>
@@ -27764,18 +27773,16 @@
       </c>
       <c r="H18" s="121" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="121" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="122" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="201">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="202">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="123" t="inlineStr">
         <is>
@@ -27808,15 +27815,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="126" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="127" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="203">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="204">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="128" t="inlineStr"/>
       <c r="L19" s="129" t="inlineStr">
@@ -27878,7 +27883,7 @@
       </c>
       <c r="K23" s="134" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="132" t="n"/>
@@ -27902,7 +27907,7 @@
       </c>
       <c r="K24" s="135" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -42481,7 +42486,7 @@
     <row r="3">
       <c r="B3" s="140" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="141" t="inlineStr">
@@ -42550,10 +42555,10 @@
       </c>
       <c r="D6" s="146" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="147" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="205" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="148" t="n">
@@ -42587,10 +42592,10 @@
       </c>
       <c r="D7" s="153" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="154" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="205" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="155" t="n">
@@ -42624,10 +42629,10 @@
       </c>
       <c r="D8" s="146" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="147" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="205" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="148" t="n">
@@ -42661,10 +42666,10 @@
       </c>
       <c r="D9" s="153" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="154" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="205" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="155" t="n">
@@ -42698,10 +42703,10 @@
       </c>
       <c r="D10" s="146" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="147" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="205" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="148" t="n">
@@ -42735,10 +42740,10 @@
       </c>
       <c r="D11" s="153" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="154" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="205" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="155" t="n">
@@ -42750,7 +42755,7 @@
       </c>
       <c r="H11" s="153" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="159" t="inlineStr">
@@ -42772,10 +42777,10 @@
       </c>
       <c r="D12" s="146" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="147" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="205" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="148" t="n">
@@ -42787,7 +42792,7 @@
       </c>
       <c r="H12" s="146" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="150" t="inlineStr">
@@ -42809,10 +42814,10 @@
       </c>
       <c r="D13" s="153" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="154" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="205" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="155" t="n">
@@ -42846,10 +42851,10 @@
       </c>
       <c r="D14" s="146" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="147" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="205" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="148" t="n">
@@ -42883,10 +42888,10 @@
       </c>
       <c r="D15" s="153" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="154" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="205" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="155" t="n">
@@ -42970,14 +42975,14 @@
     <row r="2">
       <c r="B2" s="162" t="inlineStr">
         <is>
-          <t>SEVKIYAT FIYATLAMA NAVLUN — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="163" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Lojistik müdürü, sevkiyat fiyatlandırma, filo planlama, CFO</t>
         </is>
       </c>
     </row>
@@ -43056,10 +43061,9 @@
       </c>
       <c r="C9" s="103" t="n"/>
       <c r="D9" s="103" t="n"/>
-      <c r="E9" s="170" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="206">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="103" t="n"/>
       <c r="H9" s="167" t="inlineStr">
@@ -43069,10 +43073,9 @@
       </c>
       <c r="I9" s="103" t="n"/>
       <c r="J9" s="103" t="n"/>
-      <c r="K9" s="170" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="206">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="103" t="n"/>
     </row>
@@ -43084,10 +43087,9 @@
       </c>
       <c r="C10" s="103" t="n"/>
       <c r="D10" s="103" t="n"/>
-      <c r="E10" s="171" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="207">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="103" t="n"/>
       <c r="H10" s="167" t="inlineStr">
@@ -43097,10 +43099,9 @@
       </c>
       <c r="I10" s="103" t="n"/>
       <c r="J10" s="103" t="n"/>
-      <c r="K10" s="171" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="207">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="103" t="n"/>
     </row>
@@ -43112,10 +43113,9 @@
       </c>
       <c r="C11" s="103" t="n"/>
       <c r="D11" s="103" t="n"/>
-      <c r="E11" s="171" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="208">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="103" t="n"/>
       <c r="H11" s="167" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
+++ b/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
@@ -118,7 +118,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="89">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -630,8 +630,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -809,6 +821,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1179,7 +1197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1692,6 +1710,30 @@
     </xf>
     <xf numFmtId="171" fontId="71" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4168,20 +4210,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="175" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="176" t="inlineStr">
         <is>
@@ -4446,6 +4505,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="179" t="inlineStr">
         <is>
@@ -4544,7 +4604,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4561,17 +4621,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>KAPAK — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
@@ -4584,6 +4662,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4626,6 +4705,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4654,6 +4734,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4668,6 +4749,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4677,14 +4759,15 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A9:AD9"/>
     <mergeCell ref="A8:AD8"/>
     <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A11:AD11"/>
     <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A19:P19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4701,17 +4784,34 @@
   <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="135.5" customWidth="1" min="1" max="1"/>
+    <col width="82.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4719,6 +4819,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4755,6 +4856,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4769,6 +4871,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4783,7 +4886,7 @@
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4799,23 +4902,36 @@
   <dimension ref="A1:AD1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="39.5" customWidth="1" min="1" max="1"/>
+    <col width="23.5" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>GIRDI — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Sevkiyat ve hat yatırımı girdileri</t>
         </is>
@@ -5046,6 +5162,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
@@ -5079,6 +5196,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -11299,8 +11417,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="22">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Geçersiz" error="Listeden seçin." promptTitle="Araç tipi" prompt="TIR, Kamyon veya Panelvan seçin." type="list" errorStyle="stop">
@@ -11420,15 +11539,24 @@
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>HAMMADDE — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Maliyet kalem kartı — hammadde / işçilik / ambalaj / genel gider</t>
         </is>
@@ -11441,6 +11569,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
@@ -17733,8 +17862,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="F7:F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Negatif olamaz." promptTitle="Fiyat/fire" prompt="0 ve üzeri sayı." type="decimal" errorStyle="stop" operator="between">
@@ -17764,30 +17893,40 @@
   <dimension ref="A1:AD1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23.5" customWidth="1" min="1" max="1"/>
+    <col width="20.5" customWidth="1" min="2" max="2"/>
+    <col width="15.5" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12.5" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="18.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>RECETE — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Navlun maliyet bileşim reçetesi — toplam %100 ± tolerans</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
@@ -23989,7 +24128,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="B14">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -24053,17 +24192,29 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>MOTOR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Navlun maliyet + hat yatırım motoru</t>
         </is>
@@ -24076,6 +24227,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
@@ -26096,8 +26248,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="G43">
@@ -26434,22 +26586,40 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>FIYATLAMA — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Fiyat önerisi ve rakip bandı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -26505,6 +26675,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
@@ -26538,8 +26709,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B13">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -26578,29 +26750,42 @@
   <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26.5" customWidth="1" min="1" max="1"/>
+    <col width="14.5" customWidth="1" min="2" max="2"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
+    <col width="16.5" customWidth="1" min="4" max="4"/>
+    <col width="17.5" customWidth="1" min="5" max="5"/>
+    <col width="18.5" customWidth="1" min="6" max="6"/>
+    <col width="15.5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>VARYANS — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Reçete versiyon varyans köprüsü (V0 → V1)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -26758,6 +26943,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -26782,9 +26968,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:G12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G9">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
@@ -26815,30 +27002,40 @@
   <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15.5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>VARSAYIMLAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Varsayımlar — her satırda kaynak ve güven</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
@@ -27195,8 +27392,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H13">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -27235,24 +27433,39 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>FINANSMAN — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Finansman senaryoları — OZ_KAYNAK ve KREDI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -27326,6 +27539,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -27361,9 +27575,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="E6:E7">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
@@ -27384,22 +27599,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="77.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27433,6 +27649,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="102" t="inlineStr">
         <is>
@@ -27563,6 +27780,7 @@
       <c r="L9" s="103" t="n"/>
       <c r="M9" s="103" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="96" t="inlineStr">
         <is>
@@ -27592,6 +27810,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="119" t="inlineStr">
         <is>
@@ -27846,6 +28065,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="130" t="inlineStr">
         <is>
@@ -27934,13 +28154,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="211" t="n"/>
+      <c r="H26" s="211" t="n"/>
+      <c r="I26" s="212" t="n"/>
       <c r="K26" s="139" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="213" t="n"/>
+      <c r="G27" s="214" t="n"/>
+      <c r="H27" s="214" t="n"/>
+      <c r="I27" s="215" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -27961,28 +28189,42 @@
   <dimension ref="A1:AN33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="29.5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>SENARYO — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Senaryo motoru — iyimser / baz / kötümser + tornado</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -28111,6 +28353,7 @@
         <v>650000</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -28133,6 +28376,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="45" t="inlineStr">
         <is>
@@ -28242,6 +28486,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
@@ -28294,6 +28539,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -28378,8 +28624,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D8">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="2">
@@ -28409,24 +28656,42 @@
   <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="89.5" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>KARAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Hat yatırım / navlun karar kapısı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="49" t="inlineStr">
         <is>
@@ -28449,6 +28714,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -28493,6 +28759,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
@@ -28515,6 +28782,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -28524,10 +28792,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -28581,17 +28850,34 @@
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>KANIT RAPORU — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>KANIT RAPORU — Sevkiyat Fiyatlama &amp; Navlun</t>
         </is>
@@ -28604,6 +28890,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
@@ -28648,6 +28935,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
@@ -28714,6 +29002,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
         <is>
@@ -28736,6 +29025,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
@@ -28747,6 +29037,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
@@ -28758,6 +29049,8 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
@@ -28774,6 +29067,8 @@
       </c>
       <c r="B27" s="63" t="inlineStr"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
@@ -28783,10 +29078,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B26:B27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Uzun" error="En fazla 80 karakter." promptTitle="İmza" prompt="Ad soyad yazın (opsiyonel)." type="textLength" errorStyle="stop" operator="lessThanOrEqual">
@@ -28819,18 +29115,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="70.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>KONTROLLER — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Dosya sağlık kontrolleri</t>
         </is>
@@ -28936,6 +29249,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
@@ -28949,8 +29263,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B12">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -28986,31 +29301,42 @@
   <dimension ref="A1:AD1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18.5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16.5" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>ORNEK VERI — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Örnek sevkiyat satırları</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
@@ -35194,8 +35520,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B6:B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Listeden." promptTitle="Araç" prompt="Araç tipi seçin." type="list" errorStyle="stop">
@@ -35221,22 +35548,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12.5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>LISTELER — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -35244,6 +35586,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -35325,7 +35668,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35342,28 +35685,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="23.5" customWidth="1" min="6" max="6"/>
+    <col width="23.5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>AYARLAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Parametreler ve birim dönüşüm tablosu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -36366,6 +36722,8 @@
         <v>46245</v>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39">
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -36373,6 +36731,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
@@ -42302,8 +42661,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B8:B36" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="Negatif olamaz." promptTitle="Parametre" prompt="Sayısal parametre." type="decimal" errorStyle="stop" operator="between">
@@ -42334,22 +42694,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>KILAVUZ — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="228" t="inlineStr">
         <is>
           <t>Kullanım kılavuzu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -42436,7 +42815,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A10:L10"/>
@@ -42447,9 +42826,10 @@
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A12:L12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42462,18 +42842,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42483,12 +42864,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="140" t="inlineStr">
         <is>
           <t>🔍  SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="216" t="n"/>
+      <c r="D3" s="216" t="n"/>
+      <c r="E3" s="217" t="n"/>
       <c r="G3" s="141" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -42500,6 +42885,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="143" t="inlineStr">
         <is>
@@ -42912,22 +43298,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="160" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="128" t="n"/>
-      <c r="D17" s="128" t="n"/>
       <c r="E17" s="161">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="128" t="n"/>
-      <c r="G17" s="128" t="n"/>
-      <c r="H17" s="128" t="n"/>
-      <c r="I17" s="128" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -42948,7 +43329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42993,25 +43374,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="165" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="103" t="n"/>
-      <c r="D6" s="103" t="n"/>
-      <c r="E6" s="103" t="n"/>
-      <c r="F6" s="103" t="n"/>
+      <c r="C6" s="216" t="n"/>
+      <c r="D6" s="216" t="n"/>
+      <c r="E6" s="216" t="n"/>
+      <c r="F6" s="217" t="n"/>
       <c r="H6" s="166" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="103" t="n"/>
-      <c r="J6" s="103" t="n"/>
-      <c r="K6" s="103" t="n"/>
-      <c r="L6" s="103" t="n"/>
+      <c r="I6" s="216" t="n"/>
+      <c r="J6" s="216" t="n"/>
+      <c r="K6" s="216" t="n"/>
+      <c r="L6" s="217" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="103" t="n"/>
@@ -43162,32 +43544,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="103" t="n"/>
-      <c r="D14" s="103" t="n"/>
-      <c r="E14" s="103" t="n"/>
-      <c r="F14" s="103" t="n"/>
+      <c r="C14" s="218" t="n"/>
+      <c r="D14" s="218" t="n"/>
+      <c r="E14" s="218" t="n"/>
+      <c r="F14" s="219" t="n"/>
       <c r="H14" s="173" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="103" t="n"/>
-      <c r="J14" s="103" t="n"/>
-      <c r="K14" s="103" t="n"/>
-      <c r="L14" s="103" t="n"/>
+      <c r="I14" s="220" t="n"/>
+      <c r="J14" s="220" t="n"/>
+      <c r="K14" s="220" t="n"/>
+      <c r="L14" s="221" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="103" t="n"/>
-      <c r="C15" s="103" t="n"/>
-      <c r="D15" s="103" t="n"/>
-      <c r="E15" s="103" t="n"/>
-      <c r="F15" s="103" t="n"/>
-      <c r="H15" s="103" t="n"/>
-      <c r="I15" s="103" t="n"/>
-      <c r="J15" s="103" t="n"/>
-      <c r="K15" s="103" t="n"/>
-      <c r="L15" s="103" t="n"/>
-    </row>
+      <c r="B15" s="222" t="n"/>
+      <c r="C15" s="223" t="n"/>
+      <c r="D15" s="223" t="n"/>
+      <c r="E15" s="223" t="n"/>
+      <c r="F15" s="224" t="n"/>
+      <c r="H15" s="225" t="n"/>
+      <c r="I15" s="226" t="n"/>
+      <c r="J15" s="226" t="n"/>
+      <c r="K15" s="226" t="n"/>
+      <c r="L15" s="227" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="83" t="inlineStr">
         <is>
@@ -43195,6 +43578,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="130" t="inlineStr">
         <is>
@@ -43269,25 +43653,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="180" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="181" t="inlineStr">
         <is>
@@ -43747,7 +44143,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43760,22 +44156,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="183" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="184" t="inlineStr">
         <is>
@@ -44487,7 +44898,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44500,24 +44911,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="188" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="189" t="inlineStr">
         <is>
@@ -45160,7 +45584,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45173,24 +45597,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="192" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="193" t="inlineStr">
         <is>
@@ -45705,7 +46142,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45718,23 +46155,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="195" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="209" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="210" t="n"/>
+      <c r="C1" s="210" t="n"/>
+      <c r="D1" s="210" t="n"/>
+      <c r="E1" s="210" t="n"/>
+      <c r="F1" s="210" t="n"/>
+      <c r="G1" s="210" t="n"/>
+      <c r="H1" s="210" t="n"/>
+      <c r="I1" s="210" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="196" t="inlineStr">
         <is>
@@ -46281,7 +46732,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
+++ b/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
@@ -4210,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4231,14 +4231,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -4617,7 +4609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -4638,14 +4630,6 @@
           <t>KAPAK — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -4781,7 +4765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135.5" customWidth="1" min="1" max="1"/>
@@ -4802,14 +4786,6 @@
           <t>HIZLI BASLANGIC — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -4899,7 +4875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:I1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.5" customWidth="1" min="1" max="1"/>
@@ -4920,14 +4896,6 @@
           <t>GIRDI — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -11524,7 +11492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:J1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11545,14 +11513,6 @@
           <t>HAMMADDE — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -17890,7 +17850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:H1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.5" customWidth="1" min="1" max="1"/>
@@ -17910,13 +17870,6 @@
           <t>RECETE — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -24182,7 +24135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD66"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -24203,14 +24156,6 @@
           <t>MOTOR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -25661,7 +25606,7 @@
         </is>
       </c>
       <c r="C49" s="42">
-        <f>IFERROR(IF(G47="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G47="YAPILIR","NPV pozitif ve bileşim tutarlı; hat yatırımı uygun.",IF(G47="DIKKAT","NPV dikkat bandında; yakıt/dönüş yükünü gözden geçirin.","NPV negatif veya bileşim sapması; kötümser/bazda YATIRIM YAPMA."))),"")</f>
+        <f>IFERROR(IF(G47="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G47="YAPILIR","NPV pozitif AND bileşim tutarlı; hat yatırımı uygun.",IF(G47="DIKKAT","NPV dikkat bandında; yakıt/dönüş yükünü gözden geçirin.","NPV negatif veya bileşim sapması; kötümser/bazda YATIRIM YAPMA."))),"")</f>
         <v/>
       </c>
       <c r="D49" s="37" t="inlineStr">
@@ -25680,7 +25625,7 @@
         </is>
       </c>
       <c r="G49" s="43">
-        <f>IFERROR(IF(G47="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G47="YAPILIR","NPV pozitif ve bileşim tutarlı; hat yatırımı uygun.",IF(G47="DIKKAT","NPV dikkat bandında; yakıt/dönüş yükünü gözden geçirin.","NPV negatif veya bileşim sapması; kötümser/bazda YATIRIM YAPMA."))),"")</f>
+        <f>IFERROR(IF(G47="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G47="YAPILIR","NPV pozitif AND bileşim tutarlı; hat yatırımı uygun.",IF(G47="DIKKAT","NPV dikkat bandında; yakıt/dönüş yükünü gözden geçirin.","NPV negatif veya bileşim sapması; kötümser/bazda YATIRIM YAPMA."))),"")</f>
         <v/>
       </c>
     </row>
@@ -26581,7 +26526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -26602,14 +26547,6 @@
           <t>FIYATLAMA — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -26747,7 +26684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.5" customWidth="1" min="1" max="1"/>
@@ -26768,14 +26705,6 @@
           <t>VARYANS — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -26999,7 +26928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.5" customWidth="1" min="1" max="1"/>
@@ -27019,13 +26948,6 @@
           <t>VARSAYIMLAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -27427,7 +27349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -27448,14 +27370,6 @@
           <t>FINANSMAN — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -27599,7 +27513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27730,7 +27644,7 @@
       <c r="I7" s="103" t="n"/>
       <c r="J7" s="103" t="n"/>
       <c r="K7" s="114">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="103" t="n"/>
@@ -28035,11 +27949,11 @@
         </is>
       </c>
       <c r="I19" s="203">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="204">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="128" t="inlineStr"/>
@@ -28186,7 +28100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.5" customWidth="1" min="1" max="1"/>
@@ -28207,14 +28121,6 @@
           <t>SENARYO — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -28653,7 +28559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="89.5" customWidth="1" min="1" max="1"/>
@@ -28674,14 +28580,6 @@
           <t>KARAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -28793,9 +28691,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="4">
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
@@ -28845,7 +28743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -28866,14 +28764,6 @@
           <t>KANIT RAPORU — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -29079,10 +28969,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B19:H19"/>
     <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B19:H19"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B26:B27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Uzun" error="En fazla 80 karakter." promptTitle="İmza" prompt="Ad soyad yazın (opsiyonel)." type="textLength" errorStyle="stop" operator="lessThanOrEqual">
@@ -29111,7 +29001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -29132,14 +29022,6 @@
           <t>KONTROLLER — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -29298,7 +29180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:I1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" min="1" max="1"/>
@@ -29319,14 +29201,6 @@
           <t>ORNEK VERI — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -35548,7 +35422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -35569,14 +35443,6 @@
           <t>LISTELER — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -35681,7 +35547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1004"/>
+  <dimension ref="A1:I1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35702,14 +35568,6 @@
           <t>AYARLAR — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -42690,7 +42548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -42711,14 +42569,6 @@
           <t>KILAVUZ — Sevkiyat Fiyatlama &amp; Navlun Maliyet Motoru</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -42842,7 +42692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -43306,7 +43156,7 @@
         </is>
       </c>
       <c r="E17" s="161">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -43329,7 +43179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -43496,7 +43346,7 @@
       <c r="C11" s="103" t="n"/>
       <c r="D11" s="103" t="n"/>
       <c r="E11" s="208">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="103" t="n"/>
@@ -43653,7 +43503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -43674,14 +43524,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -44156,7 +43998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44177,14 +44019,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -44911,7 +44745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -44932,14 +44766,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -45597,7 +45423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -45618,14 +45444,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -46155,7 +45973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -46176,14 +45994,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="210" t="n"/>
-      <c r="C1" s="210" t="n"/>
-      <c r="D1" s="210" t="n"/>
-      <c r="E1" s="210" t="n"/>
-      <c r="F1" s="210" t="n"/>
-      <c r="G1" s="210" t="n"/>
-      <c r="H1" s="210" t="n"/>
-      <c r="I1" s="210" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
+++ b/EXCELARSIV_PRODUCTS/sevkiyat-fiyatlama-navlun/SevkiyatFiyatlamaNavlun.xlsx
@@ -118,7 +118,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="91">
+  <fonts count="126">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -642,8 +642,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -829,8 +1035,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1193,11 +1423,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="326">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1734,6 +2306,235 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="17" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="17" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="17" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="17" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="94" fillId="17" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="96" fillId="17" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="94" fillId="17" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="17" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="44" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="69" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="44" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="69" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="108" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="109" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="6" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="16" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="17" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="11" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="10" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="17" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="17" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="111" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="122" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="122" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="17" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="11" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="10" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="17" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="17" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4232,7 +5033,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="176" t="inlineStr">
         <is>
@@ -4497,7 +5297,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="179" t="inlineStr">
         <is>
@@ -4631,7 +5430,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -4646,7 +5444,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4689,7 +5486,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4718,7 +5514,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4733,7 +5528,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4787,7 +5581,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4795,7 +5588,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4832,7 +5624,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4847,7 +5638,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4897,7 +5687,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -5130,7 +5919,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
@@ -5164,7 +5952,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -11514,7 +12301,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -11529,7 +12315,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
@@ -17871,7 +18656,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -17879,7 +18663,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
@@ -24157,7 +24940,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -24172,7 +24954,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
@@ -26548,7 +27329,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -26556,7 +27336,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -26612,7 +27391,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
@@ -26706,7 +27484,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -26714,7 +27491,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -26872,7 +27648,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -26949,7 +27724,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -26957,7 +27731,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
@@ -27371,7 +28144,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -27379,7 +28151,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -27453,7 +28224,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -27516,554 +28286,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="77.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="229" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="98" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="230" t="inlineStr">
         <is>
           <t>SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU</t>
         </is>
       </c>
-      <c r="L2" s="99" t="inlineStr">
+      <c r="L2" s="231" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="100" t="inlineStr">
+      <c r="M2" s="232" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="101" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="233" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: Lojistik müdürü, sevkiyat fiyatlandırma, filo planlama, CFO · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="102" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="234" t="inlineStr">
         <is>
           <t>NAVLUN BIRIM MALIYET</t>
         </is>
       </c>
-      <c r="C5" s="103" t="n"/>
-      <c r="D5" s="104" t="inlineStr">
+      <c r="C5" s="235" t="n"/>
+      <c r="D5" s="236" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="105" t="inlineStr">
+      <c r="E5" s="237" t="inlineStr">
         <is>
           <t>DÖNÜŞ YÜKÜ KATKISI</t>
         </is>
       </c>
-      <c r="F5" s="103" t="n"/>
-      <c r="G5" s="106" t="inlineStr">
+      <c r="F5" s="235" t="n"/>
+      <c r="G5" s="238" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="102" t="inlineStr">
+      <c r="H5" s="239" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="103" t="n"/>
-      <c r="J5" s="107" t="inlineStr">
+      <c r="I5" s="235" t="n"/>
+      <c r="J5" s="240" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="108" t="inlineStr">
+      <c r="K5" s="241" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="103" t="n"/>
-      <c r="M5" s="104" t="inlineStr">
+      <c r="L5" s="235" t="n"/>
+      <c r="M5" s="242" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="109" t="n"/>
-      <c r="C6" s="103" t="n"/>
-      <c r="D6" s="103" t="n"/>
-      <c r="E6" s="110" t="n"/>
-      <c r="F6" s="103" t="n"/>
-      <c r="G6" s="103" t="n"/>
-      <c r="H6" s="109" t="n"/>
-      <c r="I6" s="103" t="n"/>
-      <c r="J6" s="103" t="n"/>
-      <c r="K6" s="111" t="n"/>
-      <c r="L6" s="103" t="n"/>
-      <c r="M6" s="103" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="199">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="243" t="n"/>
+      <c r="C6" s="244" t="n"/>
+      <c r="D6" s="245" t="n"/>
+      <c r="E6" s="246" t="n"/>
+      <c r="F6" s="244" t="n"/>
+      <c r="G6" s="245" t="n"/>
+      <c r="H6" s="247" t="n"/>
+      <c r="I6" s="244" t="n"/>
+      <c r="J6" s="245" t="n"/>
+      <c r="K6" s="248" t="n"/>
+      <c r="L6" s="244" t="n"/>
+      <c r="M6" s="245" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="249">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="103" t="n"/>
-      <c r="D7" s="103" t="n"/>
-      <c r="E7" s="200">
+      <c r="C7" s="244" t="n"/>
+      <c r="D7" s="245" t="n"/>
+      <c r="E7" s="250">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="103" t="n"/>
-      <c r="G7" s="103" t="n"/>
-      <c r="H7" s="199">
+      <c r="F7" s="244" t="n"/>
+      <c r="G7" s="245" t="n"/>
+      <c r="H7" s="251">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="103" t="n"/>
-      <c r="J7" s="103" t="n"/>
-      <c r="K7" s="114">
+      <c r="I7" s="244" t="n"/>
+      <c r="J7" s="245" t="n"/>
+      <c r="K7" s="252">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="103" t="n"/>
-      <c r="M7" s="103" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="109" t="n"/>
-      <c r="C8" s="103" t="n"/>
-      <c r="D8" s="103" t="n"/>
-      <c r="E8" s="110" t="n"/>
-      <c r="F8" s="103" t="n"/>
-      <c r="G8" s="103" t="n"/>
-      <c r="H8" s="109" t="n"/>
-      <c r="I8" s="103" t="n"/>
-      <c r="J8" s="103" t="n"/>
-      <c r="K8" s="111" t="n"/>
-      <c r="L8" s="103" t="n"/>
-      <c r="M8" s="103" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="115" t="inlineStr">
+      <c r="L7" s="244" t="n"/>
+      <c r="M7" s="245" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="243" t="n"/>
+      <c r="C8" s="244" t="n"/>
+      <c r="D8" s="245" t="n"/>
+      <c r="E8" s="246" t="n"/>
+      <c r="F8" s="244" t="n"/>
+      <c r="G8" s="245" t="n"/>
+      <c r="H8" s="247" t="n"/>
+      <c r="I8" s="244" t="n"/>
+      <c r="J8" s="245" t="n"/>
+      <c r="K8" s="248" t="n"/>
+      <c r="L8" s="244" t="n"/>
+      <c r="M8" s="245" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="253" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="103" t="n"/>
-      <c r="D9" s="103" t="n"/>
-      <c r="E9" s="116" t="inlineStr">
+      <c r="C9" s="254" t="n"/>
+      <c r="D9" s="255" t="n"/>
+      <c r="E9" s="256" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="103" t="n"/>
-      <c r="G9" s="103" t="n"/>
-      <c r="H9" s="115" t="inlineStr">
+      <c r="F9" s="254" t="n"/>
+      <c r="G9" s="255" t="n"/>
+      <c r="H9" s="257" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="103" t="n"/>
-      <c r="J9" s="103" t="n"/>
-      <c r="K9" s="117" t="inlineStr">
+      <c r="I9" s="254" t="n"/>
+      <c r="J9" s="255" t="n"/>
+      <c r="K9" s="258" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="103" t="n"/>
-      <c r="M9" s="103" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="96" t="inlineStr">
+      <c r="L9" s="254" t="n"/>
+      <c r="M9" s="255" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="259" t="inlineStr">
         <is>
           <t>SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="118" t="inlineStr">
+      <c r="F11" s="260" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="96" t="inlineStr">
+      <c r="H11" s="259" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="95" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="95" t="inlineStr">
+      <c r="H12" s="101" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="119" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="261" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="119" t="inlineStr">
+      <c r="C14" s="261" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="119" t="inlineStr">
+      <c r="D14" s="261" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="119" t="inlineStr">
+      <c r="E14" s="261" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="120" t="inlineStr">
+      <c r="H14" s="262" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="120" t="inlineStr">
+      <c r="I14" s="263" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="120" t="inlineStr">
+      <c r="J14" s="263" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="120" t="inlineStr">
+      <c r="K14" s="263" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="120" t="inlineStr">
+      <c r="L14" s="263" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="95" t="inlineStr">
+      <c r="M14" s="263" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="264" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="C15" s="264" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="95" t="n">
+      <c r="D15" s="264" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="95" t="n">
+      <c r="E15" s="264" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="121" t="inlineStr">
+      <c r="H15" s="265" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="201">
+      <c r="I15" s="266">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="202">
+      <c r="J15" s="267">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="123" t="inlineStr">
+      <c r="K15" s="268" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="107" t="inlineStr">
+      <c r="L15" s="269" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="95" t="inlineStr">
+      <c r="M15" s="270" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="271" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="95" t="n">
+      <c r="C16" s="271" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="95" t="n">
+      <c r="D16" s="271" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="95" t="n">
+      <c r="E16" s="271" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="121" t="inlineStr">
+      <c r="H16" s="272" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="201">
+      <c r="I16" s="273">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="202">
+      <c r="J16" s="274">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="123" t="inlineStr">
+      <c r="K16" s="275" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="104" t="inlineStr">
+      <c r="L16" s="276" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="95" t="inlineStr">
+      <c r="M16" s="277" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="264" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="95" t="n">
+      <c r="C17" s="264" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="95" t="n">
+      <c r="D17" s="264" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="95" t="n">
+      <c r="E17" s="264" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="121" t="inlineStr">
+      <c r="H17" s="265" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="266">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="267">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="123" t="inlineStr">
+      <c r="K17" s="268" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="124" t="inlineStr">
+      <c r="L17" s="278" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="95" t="inlineStr">
+      <c r="M17" s="270" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="271" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="95" t="n">
+      <c r="C18" s="271" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="95" t="n">
+      <c r="D18" s="271" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="95" t="n">
+      <c r="E18" s="271" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="121" t="inlineStr">
+      <c r="H18" s="272" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="201">
+      <c r="I18" s="273">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="202">
+      <c r="J18" s="274">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="123" t="inlineStr">
+      <c r="K18" s="275" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="107" t="inlineStr">
+      <c r="L18" s="279" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="95" t="inlineStr">
+      <c r="M18" s="277" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="264" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="95" t="n">
+      <c r="C19" s="264" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="95" t="n">
+      <c r="D19" s="264" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="95" t="n">
+      <c r="E19" s="264" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="125" t="inlineStr">
+      <c r="H19" s="280" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="203">
+      <c r="I19" s="281">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="204">
+      <c r="J19" s="282">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="128" t="inlineStr"/>
-      <c r="L19" s="129" t="inlineStr">
+      <c r="K19" s="283" t="inlineStr"/>
+      <c r="L19" s="284" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="95" t="inlineStr">
+      <c r="M19" s="284" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="271" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="95" t="n">
+      <c r="C20" s="271" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="95" t="n">
+      <c r="D20" s="271" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="95" t="n">
+      <c r="E20" s="271" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="130" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="285" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="130" t="inlineStr">
+      <c r="C22" s="235" t="n"/>
+      <c r="D22" s="235" t="n"/>
+      <c r="E22" s="286" t="n"/>
+      <c r="F22" s="285" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="131" t="inlineStr">
+      <c r="G22" s="235" t="n"/>
+      <c r="H22" s="235" t="n"/>
+      <c r="I22" s="286" t="n"/>
+      <c r="K22" s="287" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="132" t="n"/>
-      <c r="M22" s="132" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="80" t="inlineStr">
+      <c r="L22" s="288" t="n"/>
+      <c r="M22" s="289" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="290" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="95" t="inlineStr">
+      <c r="C23" s="244" t="n"/>
+      <c r="D23" s="244" t="n"/>
+      <c r="E23" s="245" t="n"/>
+      <c r="F23" s="291" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="133" t="inlineStr">
+      <c r="G23" s="244" t="n"/>
+      <c r="H23" s="244" t="n"/>
+      <c r="I23" s="292" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="134" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="132" t="n"/>
-      <c r="M23" s="132" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="81" t="inlineStr">
+      <c r="K23" s="293" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="294" t="n"/>
+      <c r="M23" s="295" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="296" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="95" t="inlineStr">
+      <c r="C24" s="244" t="n"/>
+      <c r="D24" s="244" t="n"/>
+      <c r="E24" s="245" t="n"/>
+      <c r="F24" s="291" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="133" t="inlineStr">
+      <c r="G24" s="244" t="n"/>
+      <c r="H24" s="244" t="n"/>
+      <c r="I24" s="292" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="135" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="136" t="inlineStr">
+      <c r="K24" s="297" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="298" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="80" t="inlineStr">
+      <c r="C25" s="244" t="n"/>
+      <c r="D25" s="244" t="n"/>
+      <c r="E25" s="245" t="n"/>
+      <c r="F25" s="269" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="137" t="inlineStr">
+      <c r="G25" s="299" t="n"/>
+      <c r="H25" s="299" t="n"/>
+      <c r="I25" s="299" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="300" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="138" t="inlineStr">
+      <c r="C26" s="244" t="n"/>
+      <c r="D26" s="244" t="n"/>
+      <c r="E26" s="245" t="n"/>
+      <c r="F26" s="301" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -28071,23 +28872,29 @@
       <c r="G26" s="211" t="n"/>
       <c r="H26" s="211" t="n"/>
       <c r="I26" s="212" t="n"/>
-      <c r="K26" s="139" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="302" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="303" t="n"/>
+      <c r="C27" s="254" t="n"/>
+      <c r="D27" s="254" t="n"/>
+      <c r="E27" s="255" t="n"/>
       <c r="F27" s="213" t="n"/>
       <c r="G27" s="214" t="n"/>
       <c r="H27" s="214" t="n"/>
       <c r="I27" s="215" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28122,7 +28929,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -28130,7 +28936,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -28259,7 +29064,6 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -28282,7 +29086,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="45" t="inlineStr">
         <is>
@@ -28392,7 +29195,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
@@ -28445,7 +29247,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -28581,7 +29382,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -28589,7 +29389,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="49" t="inlineStr">
         <is>
@@ -28612,7 +29411,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -28657,7 +29455,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
@@ -28680,7 +29477,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -28765,7 +29561,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -28780,7 +29575,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
@@ -28825,7 +29619,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
@@ -28892,7 +29685,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
         <is>
@@ -28915,7 +29707,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
@@ -28927,7 +29718,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
@@ -28939,8 +29729,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
@@ -28957,8 +29745,6 @@
       </c>
       <c r="B27" s="63" t="inlineStr"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
@@ -29023,7 +29809,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -29131,7 +29916,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="29" t="inlineStr">
         <is>
@@ -29202,7 +29986,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -29210,7 +29993,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
@@ -35444,7 +36226,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -35452,7 +36233,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -35569,7 +36349,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -35577,7 +36356,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -36580,8 +37358,6 @@
         <v>46245</v>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39">
       <c r="D39" s="5" t="inlineStr">
         <is>
@@ -36589,7 +37365,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
@@ -42570,7 +43345,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="228" t="inlineStr">
         <is>
@@ -42578,7 +43352,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -42714,7 +43487,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="140" t="inlineStr">
         <is>
@@ -42735,7 +43507,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="143" t="inlineStr">
         <is>
@@ -43148,7 +43919,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="160" t="inlineStr">
         <is>
@@ -43179,54 +43949,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="229" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="162" t="inlineStr">
         <is>
           <t>SEVKIYAT FIYATLAMA &amp; NAVLUN MALIYET MOTORU — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="163" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="304" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Lojistik müdürü, sevkiyat fiyatlandırma, filo planlama, CFO</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="164" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="305" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="165" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="306" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -43235,7 +44006,7 @@
       <c r="D6" s="216" t="n"/>
       <c r="E6" s="216" t="n"/>
       <c r="F6" s="217" t="n"/>
-      <c r="H6" s="166" t="inlineStr">
+      <c r="H6" s="307" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -43245,151 +44016,151 @@
       <c r="K6" s="216" t="n"/>
       <c r="L6" s="217" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="103" t="n"/>
-      <c r="C7" s="103" t="n"/>
-      <c r="D7" s="103" t="n"/>
-      <c r="E7" s="103" t="n"/>
-      <c r="F7" s="103" t="n"/>
-      <c r="H7" s="103" t="n"/>
-      <c r="I7" s="103" t="n"/>
-      <c r="J7" s="103" t="n"/>
-      <c r="K7" s="103" t="n"/>
-      <c r="L7" s="103" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="167" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="308" t="n"/>
+      <c r="C7" s="244" t="n"/>
+      <c r="D7" s="244" t="n"/>
+      <c r="E7" s="244" t="n"/>
+      <c r="F7" s="309" t="n"/>
+      <c r="H7" s="310" t="n"/>
+      <c r="I7" s="244" t="n"/>
+      <c r="J7" s="244" t="n"/>
+      <c r="K7" s="244" t="n"/>
+      <c r="L7" s="311" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="312" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="103" t="n"/>
-      <c r="D8" s="103" t="n"/>
-      <c r="E8" s="168" t="inlineStr">
+      <c r="C8" s="244" t="n"/>
+      <c r="D8" s="244" t="n"/>
+      <c r="E8" s="313" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="103" t="n"/>
-      <c r="H8" s="167" t="inlineStr">
+      <c r="F8" s="309" t="n"/>
+      <c r="H8" s="314" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="103" t="n"/>
-      <c r="J8" s="103" t="n"/>
-      <c r="K8" s="169" t="inlineStr">
+      <c r="I8" s="244" t="n"/>
+      <c r="J8" s="244" t="n"/>
+      <c r="K8" s="315" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="103" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="167" t="inlineStr">
+      <c r="L8" s="311" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="312" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="103" t="n"/>
-      <c r="D9" s="103" t="n"/>
-      <c r="E9" s="206">
+      <c r="C9" s="244" t="n"/>
+      <c r="D9" s="244" t="n"/>
+      <c r="E9" s="316">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="103" t="n"/>
-      <c r="H9" s="167" t="inlineStr">
+      <c r="F9" s="309" t="n"/>
+      <c r="H9" s="314" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="103" t="n"/>
-      <c r="J9" s="103" t="n"/>
-      <c r="K9" s="206">
+      <c r="I9" s="244" t="n"/>
+      <c r="J9" s="244" t="n"/>
+      <c r="K9" s="316">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="103" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="167" t="inlineStr">
+      <c r="L9" s="311" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="312" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="103" t="n"/>
-      <c r="D10" s="103" t="n"/>
-      <c r="E10" s="207">
+      <c r="C10" s="244" t="n"/>
+      <c r="D10" s="244" t="n"/>
+      <c r="E10" s="317">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="103" t="n"/>
-      <c r="H10" s="167" t="inlineStr">
+      <c r="F10" s="309" t="n"/>
+      <c r="H10" s="314" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="103" t="n"/>
-      <c r="J10" s="103" t="n"/>
-      <c r="K10" s="207">
+      <c r="I10" s="244" t="n"/>
+      <c r="J10" s="244" t="n"/>
+      <c r="K10" s="317">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="103" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="167" t="inlineStr">
+      <c r="L10" s="311" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="312" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="103" t="n"/>
-      <c r="D11" s="103" t="n"/>
-      <c r="E11" s="208">
+      <c r="C11" s="244" t="n"/>
+      <c r="D11" s="244" t="n"/>
+      <c r="E11" s="318">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="103" t="n"/>
-      <c r="H11" s="167" t="inlineStr">
+      <c r="F11" s="309" t="n"/>
+      <c r="H11" s="314" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="103" t="n"/>
-      <c r="J11" s="103" t="n"/>
-      <c r="K11" s="171" t="inlineStr">
+      <c r="I11" s="244" t="n"/>
+      <c r="J11" s="244" t="n"/>
+      <c r="K11" s="319" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="103" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="103" t="n"/>
-      <c r="C12" s="103" t="n"/>
-      <c r="D12" s="103" t="n"/>
-      <c r="E12" s="103" t="n"/>
-      <c r="F12" s="103" t="n"/>
-      <c r="H12" s="103" t="n"/>
-      <c r="I12" s="103" t="n"/>
-      <c r="J12" s="103" t="n"/>
-      <c r="K12" s="103" t="n"/>
-      <c r="L12" s="103" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="103" t="n"/>
-      <c r="C13" s="103" t="n"/>
-      <c r="D13" s="103" t="n"/>
-      <c r="E13" s="103" t="n"/>
-      <c r="F13" s="103" t="n"/>
-      <c r="H13" s="103" t="n"/>
-      <c r="I13" s="103" t="n"/>
-      <c r="J13" s="103" t="n"/>
-      <c r="K13" s="103" t="n"/>
-      <c r="L13" s="103" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="172" t="inlineStr">
+      <c r="L11" s="311" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="308" t="n"/>
+      <c r="C12" s="244" t="n"/>
+      <c r="D12" s="244" t="n"/>
+      <c r="E12" s="244" t="n"/>
+      <c r="F12" s="309" t="n"/>
+      <c r="H12" s="310" t="n"/>
+      <c r="I12" s="244" t="n"/>
+      <c r="J12" s="244" t="n"/>
+      <c r="K12" s="244" t="n"/>
+      <c r="L12" s="311" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="308" t="n"/>
+      <c r="C13" s="244" t="n"/>
+      <c r="D13" s="244" t="n"/>
+      <c r="E13" s="244" t="n"/>
+      <c r="F13" s="309" t="n"/>
+      <c r="H13" s="310" t="n"/>
+      <c r="I13" s="244" t="n"/>
+      <c r="J13" s="244" t="n"/>
+      <c r="K13" s="244" t="n"/>
+      <c r="L13" s="311" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="320" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -43398,7 +44169,7 @@
       <c r="D14" s="218" t="n"/>
       <c r="E14" s="218" t="n"/>
       <c r="F14" s="219" t="n"/>
-      <c r="H14" s="173" t="inlineStr">
+      <c r="H14" s="321" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -43408,7 +44179,7 @@
       <c r="K14" s="220" t="n"/>
       <c r="L14" s="221" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="222" t="n"/>
       <c r="C15" s="223" t="n"/>
       <c r="D15" s="223" t="n"/>
@@ -43420,70 +44191,185 @@
       <c r="K15" s="226" t="n"/>
       <c r="L15" s="227" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="83" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="322" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="130" t="inlineStr">
+      <c r="C17" s="235" t="n"/>
+      <c r="D17" s="235" t="n"/>
+      <c r="E17" s="235" t="n"/>
+      <c r="F17" s="235" t="n"/>
+      <c r="G17" s="235" t="n"/>
+      <c r="H17" s="235" t="n"/>
+      <c r="I17" s="235" t="n"/>
+      <c r="J17" s="235" t="n"/>
+      <c r="K17" s="235" t="n"/>
+      <c r="L17" s="286" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="323" t="n"/>
+      <c r="C18" s="244" t="n"/>
+      <c r="D18" s="244" t="n"/>
+      <c r="E18" s="244" t="n"/>
+      <c r="F18" s="244" t="n"/>
+      <c r="G18" s="244" t="n"/>
+      <c r="H18" s="244" t="n"/>
+      <c r="I18" s="244" t="n"/>
+      <c r="J18" s="244" t="n"/>
+      <c r="K18" s="244" t="n"/>
+      <c r="L18" s="245" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="324" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="174" t="inlineStr">
+      <c r="C19" s="244" t="n"/>
+      <c r="D19" s="244" t="n"/>
+      <c r="E19" s="244" t="n"/>
+      <c r="F19" s="244" t="n"/>
+      <c r="G19" s="244" t="n"/>
+      <c r="H19" s="244" t="n"/>
+      <c r="I19" s="244" t="n"/>
+      <c r="J19" s="244" t="n"/>
+      <c r="K19" s="244" t="n"/>
+      <c r="L19" s="245" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="325" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="130" t="inlineStr">
+      <c r="C20" s="244" t="n"/>
+      <c r="D20" s="244" t="n"/>
+      <c r="E20" s="244" t="n"/>
+      <c r="F20" s="244" t="n"/>
+      <c r="G20" s="244" t="n"/>
+      <c r="H20" s="244" t="n"/>
+      <c r="I20" s="244" t="n"/>
+      <c r="J20" s="244" t="n"/>
+      <c r="K20" s="244" t="n"/>
+      <c r="L20" s="245" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="324" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="174" t="inlineStr">
+      <c r="C21" s="244" t="n"/>
+      <c r="D21" s="244" t="n"/>
+      <c r="E21" s="244" t="n"/>
+      <c r="F21" s="244" t="n"/>
+      <c r="G21" s="244" t="n"/>
+      <c r="H21" s="244" t="n"/>
+      <c r="I21" s="244" t="n"/>
+      <c r="J21" s="244" t="n"/>
+      <c r="K21" s="244" t="n"/>
+      <c r="L21" s="245" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="325" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="130" t="inlineStr">
+      <c r="C22" s="244" t="n"/>
+      <c r="D22" s="244" t="n"/>
+      <c r="E22" s="244" t="n"/>
+      <c r="F22" s="244" t="n"/>
+      <c r="G22" s="244" t="n"/>
+      <c r="H22" s="244" t="n"/>
+      <c r="I22" s="244" t="n"/>
+      <c r="J22" s="244" t="n"/>
+      <c r="K22" s="244" t="n"/>
+      <c r="L22" s="245" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="324" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="174" t="inlineStr">
+      <c r="C23" s="244" t="n"/>
+      <c r="D23" s="244" t="n"/>
+      <c r="E23" s="244" t="n"/>
+      <c r="F23" s="244" t="n"/>
+      <c r="G23" s="244" t="n"/>
+      <c r="H23" s="244" t="n"/>
+      <c r="I23" s="244" t="n"/>
+      <c r="J23" s="244" t="n"/>
+      <c r="K23" s="244" t="n"/>
+      <c r="L23" s="245" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="325" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="130" t="inlineStr">
+      <c r="C24" s="244" t="n"/>
+      <c r="D24" s="244" t="n"/>
+      <c r="E24" s="244" t="n"/>
+      <c r="F24" s="244" t="n"/>
+      <c r="G24" s="244" t="n"/>
+      <c r="H24" s="244" t="n"/>
+      <c r="I24" s="244" t="n"/>
+      <c r="J24" s="244" t="n"/>
+      <c r="K24" s="244" t="n"/>
+      <c r="L24" s="245" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="324" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="174" t="inlineStr">
+      <c r="C25" s="244" t="n"/>
+      <c r="D25" s="244" t="n"/>
+      <c r="E25" s="244" t="n"/>
+      <c r="F25" s="244" t="n"/>
+      <c r="G25" s="244" t="n"/>
+      <c r="H25" s="244" t="n"/>
+      <c r="I25" s="244" t="n"/>
+      <c r="J25" s="244" t="n"/>
+      <c r="K25" s="244" t="n"/>
+      <c r="L25" s="245" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="325" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="244" t="n"/>
+      <c r="D26" s="244" t="n"/>
+      <c r="E26" s="244" t="n"/>
+      <c r="F26" s="244" t="n"/>
+      <c r="G26" s="244" t="n"/>
+      <c r="H26" s="244" t="n"/>
+      <c r="I26" s="244" t="n"/>
+      <c r="J26" s="244" t="n"/>
+      <c r="K26" s="244" t="n"/>
+      <c r="L26" s="245" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="303" t="n"/>
+      <c r="C27" s="254" t="n"/>
+      <c r="D27" s="254" t="n"/>
+      <c r="E27" s="254" t="n"/>
+      <c r="F27" s="254" t="n"/>
+      <c r="G27" s="254" t="n"/>
+      <c r="H27" s="254" t="n"/>
+      <c r="I27" s="254" t="n"/>
+      <c r="J27" s="254" t="n"/>
+      <c r="K27" s="254" t="n"/>
+      <c r="L27" s="255" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -43525,7 +44411,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="181" t="inlineStr">
         <is>
@@ -44020,7 +44905,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="184" t="inlineStr">
         <is>
@@ -44767,7 +45651,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="189" t="inlineStr">
         <is>
@@ -45445,7 +46328,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="193" t="inlineStr">
         <is>
@@ -45995,7 +46877,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="196" t="inlineStr">
         <is>
